--- a/backend/uploads/Dataset_Dummy_Clinker_3MPlan.xlsx
+++ b/backend/uploads/Dataset_Dummy_Clinker_3MPlan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adaniltd-my.sharepoint.com/personal/30087991_adani_com/Documents/Documents/OR Team/OR Projects/Active/Clinker Allocation Optimization-II/Code/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\janak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6B2A390-1726-DB44-BD2C-DD5E584464EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E58167-1608-49C4-9B6F-FF8F51823545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ClinkerDemand" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">IUGUClosingStock!$A$1:$M$133</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LogisticsIUGU!$A$1:$G$349</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,8 +37,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -46,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="81">
   <si>
     <t>IUGU CODE</t>
   </si>
@@ -287,12 +285,15 @@
   <si>
     <t># Source</t>
   </si>
+  <si>
+    <t>O</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,6 +306,13 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -339,18 +347,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -650,1489 +664,1614 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D133"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.97265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.84765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4">
         <v>222553</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4">
         <v>72369</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4">
         <v>161885</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4">
         <v>216053</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4">
         <v>142403</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="D6" s="4"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
+      <c r="B7" s="4">
+        <v>1</v>
+      </c>
+      <c r="C7" s="4">
         <v>195696</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="D7" s="4"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
+      <c r="B8" s="4">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4">
         <v>264228</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
+      <c r="B9" s="4">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4">
         <v>142297</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
+      <c r="B10" s="4">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
         <v>108302</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="4">
+        <v>1</v>
+      </c>
+      <c r="C11" s="4">
         <v>86799</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
         <v>63895</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
         <v>141200</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
         <v>212187</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="D14" s="4"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4">
         <v>189353</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4">
         <v>164015</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4">
         <v>222387</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4">
         <v>72902</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
+      <c r="B19" s="4">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4">
         <v>267588</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
+      <c r="B20" s="4">
+        <v>1</v>
+      </c>
+      <c r="C20" s="4">
         <v>231997</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
+      <c r="B21" s="4">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4">
         <v>232114</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
+      <c r="B22" s="4">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4">
         <v>208606</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
+      <c r="B23" s="4">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4">
         <v>185454</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
+      <c r="B24" s="4">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4">
         <v>164015</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
+      <c r="B25" s="4">
+        <v>1</v>
+      </c>
+      <c r="C25" s="4">
         <v>118459</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
+      <c r="B26" s="4">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4">
         <v>244150</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
+      <c r="B27" s="4">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4">
         <v>51565</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
+      <c r="B28" s="4">
+        <v>1</v>
+      </c>
+      <c r="C28" s="4">
         <v>247363</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-      <c r="C29">
+      <c r="B29" s="4">
+        <v>1</v>
+      </c>
+      <c r="C29" s="4">
         <v>273307</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30">
+      <c r="B30" s="4">
+        <v>1</v>
+      </c>
+      <c r="C30" s="4">
         <v>64083</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-      <c r="C31">
+      <c r="B31" s="4">
+        <v>1</v>
+      </c>
+      <c r="C31" s="4">
         <v>280865</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32">
+      <c r="B32" s="4">
+        <v>1</v>
+      </c>
+      <c r="C32" s="4">
         <v>124400</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="D32" s="4"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B33">
-        <v>1</v>
-      </c>
-      <c r="C33">
+      <c r="B33" s="4">
+        <v>1</v>
+      </c>
+      <c r="C33" s="4">
         <v>73775</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="D33" s="4"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34">
+      <c r="B34" s="4">
+        <v>1</v>
+      </c>
+      <c r="C34" s="4">
         <v>197269</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="D34" s="4"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B35">
-        <v>1</v>
-      </c>
-      <c r="C35">
+      <c r="B35" s="4">
+        <v>1</v>
+      </c>
+      <c r="C35" s="4">
         <v>222191</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="D35" s="4"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36">
+      <c r="B36" s="4">
+        <v>1</v>
+      </c>
+      <c r="C36" s="4">
         <v>106883</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="D36" s="4"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37">
+      <c r="B37" s="4">
+        <v>1</v>
+      </c>
+      <c r="C37" s="4">
         <v>226756</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="D37" s="4"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-      <c r="C38">
+      <c r="B38" s="4">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4">
         <v>229332</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="D38" s="4"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39">
+      <c r="B39" s="4">
+        <v>1</v>
+      </c>
+      <c r="C39" s="4">
         <v>176743</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40">
+      <c r="B40" s="4">
+        <v>1</v>
+      </c>
+      <c r="C40" s="4">
         <v>231068</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="D40" s="4"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41">
+      <c r="B41" s="4">
+        <v>1</v>
+      </c>
+      <c r="C41" s="4">
         <v>209478</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="D41" s="4"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B42">
-        <v>1</v>
-      </c>
-      <c r="C42">
+      <c r="B42" s="4">
+        <v>1</v>
+      </c>
+      <c r="C42" s="4">
         <v>200210</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="C43">
+      <c r="B43" s="4">
+        <v>1</v>
+      </c>
+      <c r="C43" s="4">
         <v>196158</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44">
+      <c r="B44" s="4">
+        <v>1</v>
+      </c>
+      <c r="C44" s="4">
         <v>241386</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="D44" s="4"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-      <c r="C45">
+      <c r="B45" s="4">
+        <v>1</v>
+      </c>
+      <c r="C45" s="4">
         <v>277367</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="D45" s="4"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B46">
-        <v>2</v>
-      </c>
-      <c r="C46">
+      <c r="B46" s="4">
+        <v>2</v>
+      </c>
+      <c r="C46" s="4">
         <v>266578</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B47">
-        <v>2</v>
-      </c>
-      <c r="C47">
+      <c r="B47" s="4">
+        <v>2</v>
+      </c>
+      <c r="C47" s="4">
         <v>148436</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B48">
-        <v>2</v>
-      </c>
-      <c r="C48">
+      <c r="B48" s="4">
+        <v>2</v>
+      </c>
+      <c r="C48" s="4">
         <v>294543</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="D48" s="4"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B49">
-        <v>2</v>
-      </c>
-      <c r="C49">
+      <c r="B49" s="4">
+        <v>2</v>
+      </c>
+      <c r="C49" s="4">
         <v>263388</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+      <c r="D49" s="4"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B50">
-        <v>2</v>
-      </c>
-      <c r="C50">
+      <c r="B50" s="4">
+        <v>2</v>
+      </c>
+      <c r="C50" s="4">
         <v>242119</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+      <c r="D50" s="4"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B51">
-        <v>2</v>
-      </c>
-      <c r="C51">
+      <c r="B51" s="4">
+        <v>2</v>
+      </c>
+      <c r="C51" s="4">
         <v>175735</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="D51" s="4"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B52">
-        <v>2</v>
-      </c>
-      <c r="C52">
+      <c r="B52" s="4">
+        <v>2</v>
+      </c>
+      <c r="C52" s="4">
         <v>208628</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+      <c r="D52" s="4"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B53">
-        <v>2</v>
-      </c>
-      <c r="C53">
+      <c r="B53" s="4">
+        <v>2</v>
+      </c>
+      <c r="C53" s="4">
         <v>266398</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+      <c r="D53" s="4"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B54">
-        <v>2</v>
-      </c>
-      <c r="C54">
+      <c r="B54" s="4">
+        <v>2</v>
+      </c>
+      <c r="C54" s="4">
         <v>277306</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="D54" s="4"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B55">
-        <v>2</v>
-      </c>
-      <c r="C55">
+      <c r="B55" s="4">
+        <v>2</v>
+      </c>
+      <c r="C55" s="4">
         <v>221636</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+      <c r="D55" s="4"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B56">
-        <v>2</v>
-      </c>
-      <c r="C56">
+      <c r="B56" s="4">
+        <v>2</v>
+      </c>
+      <c r="C56" s="4">
         <v>90017</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="D56" s="4"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B57">
-        <v>2</v>
-      </c>
-      <c r="C57">
+      <c r="B57" s="4">
+        <v>2</v>
+      </c>
+      <c r="C57" s="4">
         <v>124345</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+      <c r="D57" s="4"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B58">
-        <v>2</v>
-      </c>
-      <c r="C58">
+      <c r="B58" s="4">
+        <v>2</v>
+      </c>
+      <c r="C58" s="4">
         <v>153205</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+      <c r="D58" s="4"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B59">
-        <v>2</v>
-      </c>
-      <c r="C59">
+      <c r="B59" s="4">
+        <v>2</v>
+      </c>
+      <c r="C59" s="4">
         <v>253901</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+      <c r="D59" s="4"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="C60">
+      <c r="B60" s="4">
+        <v>2</v>
+      </c>
+      <c r="C60" s="4">
         <v>214935</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+      <c r="D60" s="4"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
-      <c r="C61">
+      <c r="B61" s="4">
+        <v>2</v>
+      </c>
+      <c r="C61" s="4">
         <v>267294</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+      <c r="D61" s="4"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B62">
-        <v>2</v>
-      </c>
-      <c r="C62">
+      <c r="B62" s="4">
+        <v>2</v>
+      </c>
+      <c r="C62" s="4">
         <v>105102</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+      <c r="D62" s="4"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63">
+      <c r="B63" s="4">
+        <v>2</v>
+      </c>
+      <c r="C63" s="4">
         <v>102398</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+      <c r="D63" s="4"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B64">
-        <v>2</v>
-      </c>
-      <c r="C64">
+      <c r="B64" s="4">
+        <v>2</v>
+      </c>
+      <c r="C64" s="4">
         <v>50816</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+      <c r="D64" s="4"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B65">
-        <v>2</v>
-      </c>
-      <c r="C65">
+      <c r="B65" s="4">
+        <v>2</v>
+      </c>
+      <c r="C65" s="4">
         <v>250634</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+      <c r="D65" s="4"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-      <c r="C66">
+      <c r="B66" s="4">
+        <v>2</v>
+      </c>
+      <c r="C66" s="4">
         <v>222050</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+      <c r="D66" s="4"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
-      <c r="C67">
+      <c r="B67" s="4">
+        <v>2</v>
+      </c>
+      <c r="C67" s="4">
         <v>143859</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+      <c r="D67" s="4"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="C68">
+      <c r="B68" s="4">
+        <v>2</v>
+      </c>
+      <c r="C68" s="4">
         <v>195183</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+      <c r="D68" s="4"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B69">
-        <v>2</v>
-      </c>
-      <c r="C69">
+      <c r="B69" s="4">
+        <v>2</v>
+      </c>
+      <c r="C69" s="4">
         <v>209619</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+      <c r="D69" s="4"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B70">
-        <v>2</v>
-      </c>
-      <c r="C70">
+      <c r="B70" s="4">
+        <v>2</v>
+      </c>
+      <c r="C70" s="4">
         <v>200504</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="D70" s="4"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B71">
-        <v>2</v>
-      </c>
-      <c r="C71">
+      <c r="B71" s="4">
+        <v>2</v>
+      </c>
+      <c r="C71" s="4">
         <v>116641</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+      <c r="D71" s="4"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B72">
-        <v>2</v>
-      </c>
-      <c r="C72">
+      <c r="B72" s="4">
+        <v>2</v>
+      </c>
+      <c r="C72" s="4">
         <v>71953</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+      <c r="D72" s="4"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B73">
-        <v>2</v>
-      </c>
-      <c r="C73">
+      <c r="B73" s="4">
+        <v>2</v>
+      </c>
+      <c r="C73" s="4">
         <v>50783</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+      <c r="D73" s="4"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B74">
-        <v>2</v>
-      </c>
-      <c r="C74">
+      <c r="B74" s="4">
+        <v>2</v>
+      </c>
+      <c r="C74" s="4">
         <v>179832</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+      <c r="D74" s="4"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B75">
-        <v>2</v>
-      </c>
-      <c r="C75">
+      <c r="B75" s="4">
+        <v>2</v>
+      </c>
+      <c r="C75" s="4">
         <v>212325</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+      <c r="D75" s="4"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B76">
-        <v>2</v>
-      </c>
-      <c r="C76">
+      <c r="B76" s="4">
+        <v>2</v>
+      </c>
+      <c r="C76" s="4">
         <v>51215</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+      <c r="D76" s="4"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B77">
-        <v>2</v>
-      </c>
-      <c r="C77">
+      <c r="B77" s="4">
+        <v>2</v>
+      </c>
+      <c r="C77" s="4">
         <v>102045</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+      <c r="D77" s="4"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B78">
-        <v>2</v>
-      </c>
-      <c r="C78">
+      <c r="B78" s="4">
+        <v>2</v>
+      </c>
+      <c r="C78" s="4">
         <v>192586</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+      <c r="D78" s="4"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B79">
-        <v>2</v>
-      </c>
-      <c r="C79">
+      <c r="B79" s="4">
+        <v>2</v>
+      </c>
+      <c r="C79" s="4">
         <v>99055</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+      <c r="D79" s="4"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B80">
-        <v>2</v>
-      </c>
-      <c r="C80">
+      <c r="B80" s="4">
+        <v>2</v>
+      </c>
+      <c r="C80" s="4">
         <v>65380</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
+      <c r="D80" s="4"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B81">
-        <v>2</v>
-      </c>
-      <c r="C81">
+      <c r="B81" s="4">
+        <v>2</v>
+      </c>
+      <c r="C81" s="4">
         <v>67992</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+      <c r="D81" s="4"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B82">
-        <v>2</v>
-      </c>
-      <c r="C82">
+      <c r="B82" s="4">
+        <v>2</v>
+      </c>
+      <c r="C82" s="4">
         <v>252304</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+      <c r="D82" s="4"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B83">
-        <v>2</v>
-      </c>
-      <c r="C83">
+      <c r="B83" s="4">
+        <v>2</v>
+      </c>
+      <c r="C83" s="4">
         <v>149210</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+      <c r="D83" s="4"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B84">
-        <v>2</v>
-      </c>
-      <c r="C84">
+      <c r="B84" s="4">
+        <v>2</v>
+      </c>
+      <c r="C84" s="4">
         <v>202505</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+      <c r="D84" s="4"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B85">
-        <v>2</v>
-      </c>
-      <c r="C85">
+      <c r="B85" s="4">
+        <v>2</v>
+      </c>
+      <c r="C85" s="4">
         <v>166301</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
+      <c r="D85" s="4"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B86">
-        <v>2</v>
-      </c>
-      <c r="C86">
+      <c r="B86" s="4">
+        <v>2</v>
+      </c>
+      <c r="C86" s="4">
         <v>287551</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+      <c r="D86" s="4"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B87">
-        <v>2</v>
-      </c>
-      <c r="C87">
+      <c r="B87" s="4">
+        <v>2</v>
+      </c>
+      <c r="C87" s="4">
         <v>51341</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
+      <c r="D87" s="4"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B88">
-        <v>2</v>
-      </c>
-      <c r="C88">
+      <c r="B88" s="4">
+        <v>2</v>
+      </c>
+      <c r="C88" s="4">
         <v>140555</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
+      <c r="D88" s="4"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B89">
-        <v>2</v>
-      </c>
-      <c r="C89">
+      <c r="B89" s="4">
+        <v>2</v>
+      </c>
+      <c r="C89" s="4">
         <v>55915</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
+      <c r="D89" s="4"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B90">
-        <v>3</v>
-      </c>
-      <c r="C90">
+      <c r="B90" s="4">
+        <v>3</v>
+      </c>
+      <c r="C90" s="4">
         <v>110358</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
+      <c r="D90" s="4"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B91">
-        <v>3</v>
-      </c>
-      <c r="C91">
+      <c r="B91" s="4">
+        <v>3</v>
+      </c>
+      <c r="C91" s="4">
         <v>104867</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+      <c r="D91" s="4"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B92">
-        <v>3</v>
-      </c>
-      <c r="C92">
+      <c r="B92" s="4">
+        <v>3</v>
+      </c>
+      <c r="C92" s="4">
         <v>186037</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+      <c r="D92" s="4"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B93">
-        <v>3</v>
-      </c>
-      <c r="C93">
+      <c r="B93" s="4">
+        <v>3</v>
+      </c>
+      <c r="C93" s="4">
         <v>198258</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
+      <c r="D93" s="4"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B94">
-        <v>3</v>
-      </c>
-      <c r="C94">
+      <c r="B94" s="4">
+        <v>3</v>
+      </c>
+      <c r="C94" s="4">
         <v>220919</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
+      <c r="D94" s="4"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B95">
-        <v>3</v>
-      </c>
-      <c r="C95">
+      <c r="B95" s="4">
+        <v>3</v>
+      </c>
+      <c r="C95" s="4">
         <v>265904</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
+      <c r="D95" s="4"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B96">
-        <v>3</v>
-      </c>
-      <c r="C96">
+      <c r="B96" s="4">
+        <v>3</v>
+      </c>
+      <c r="C96" s="4">
         <v>98934</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
+      <c r="D96" s="4"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B97">
-        <v>3</v>
-      </c>
-      <c r="C97">
+      <c r="B97" s="4">
+        <v>3</v>
+      </c>
+      <c r="C97" s="4">
         <v>164845</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
+      <c r="D97" s="4"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B98">
-        <v>3</v>
-      </c>
-      <c r="C98">
+      <c r="B98" s="4">
+        <v>3</v>
+      </c>
+      <c r="C98" s="4">
         <v>292848</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
+      <c r="D98" s="4"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B99">
-        <v>3</v>
-      </c>
-      <c r="C99">
+      <c r="B99" s="4">
+        <v>3</v>
+      </c>
+      <c r="C99" s="4">
         <v>257267</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
+      <c r="D99" s="4"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B100">
-        <v>3</v>
-      </c>
-      <c r="C100">
+      <c r="B100" s="4">
+        <v>3</v>
+      </c>
+      <c r="C100" s="4">
         <v>144996</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
+      <c r="D100" s="4"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B101">
-        <v>3</v>
-      </c>
-      <c r="C101">
+      <c r="B101" s="4">
+        <v>3</v>
+      </c>
+      <c r="C101" s="4">
         <v>146479</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
+      <c r="D101" s="4"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B102">
-        <v>3</v>
-      </c>
-      <c r="C102">
+      <c r="B102" s="4">
+        <v>3</v>
+      </c>
+      <c r="C102" s="4">
         <v>122206</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
+      <c r="D102" s="4"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B103">
-        <v>3</v>
-      </c>
-      <c r="C103">
+      <c r="B103" s="4">
+        <v>3</v>
+      </c>
+      <c r="C103" s="4">
         <v>86233</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
+      <c r="D103" s="4"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B104">
-        <v>3</v>
-      </c>
-      <c r="C104">
+      <c r="B104" s="4">
+        <v>3</v>
+      </c>
+      <c r="C104" s="4">
         <v>163201</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
+      <c r="D104" s="4"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B105">
-        <v>3</v>
-      </c>
-      <c r="C105">
+      <c r="B105" s="4">
+        <v>3</v>
+      </c>
+      <c r="C105" s="4">
         <v>230651</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
+      <c r="D105" s="4"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B106">
-        <v>3</v>
-      </c>
-      <c r="C106">
+      <c r="B106" s="4">
+        <v>3</v>
+      </c>
+      <c r="C106" s="4">
         <v>90635</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
+      <c r="D106" s="4"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B107">
-        <v>3</v>
-      </c>
-      <c r="C107">
+      <c r="B107" s="4">
+        <v>3</v>
+      </c>
+      <c r="C107" s="4">
         <v>112526</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
+      <c r="D107" s="4"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B108">
-        <v>3</v>
-      </c>
-      <c r="C108">
+      <c r="B108" s="4">
+        <v>3</v>
+      </c>
+      <c r="C108" s="4">
         <v>118548</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
+      <c r="D108" s="4"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B109">
-        <v>3</v>
-      </c>
-      <c r="C109">
+      <c r="B109" s="4">
+        <v>3</v>
+      </c>
+      <c r="C109" s="4">
         <v>283875</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
+      <c r="D109" s="4"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B110">
-        <v>3</v>
-      </c>
-      <c r="C110">
+      <c r="B110" s="4">
+        <v>3</v>
+      </c>
+      <c r="C110" s="4">
         <v>285221</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
+      <c r="D110" s="4"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B111">
-        <v>3</v>
-      </c>
-      <c r="C111">
+      <c r="B111" s="4">
+        <v>3</v>
+      </c>
+      <c r="C111" s="4">
         <v>136637</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
+      <c r="D111" s="4"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B112">
-        <v>3</v>
-      </c>
-      <c r="C112">
+      <c r="B112" s="4">
+        <v>3</v>
+      </c>
+      <c r="C112" s="4">
         <v>59465</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
+      <c r="D112" s="4"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B113">
-        <v>3</v>
-      </c>
-      <c r="C113">
+      <c r="B113" s="4">
+        <v>3</v>
+      </c>
+      <c r="C113" s="4">
         <v>216951</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
+      <c r="D113" s="4"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B114">
-        <v>3</v>
-      </c>
-      <c r="C114">
+      <c r="B114" s="4">
+        <v>3</v>
+      </c>
+      <c r="C114" s="4">
         <v>132503</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
+      <c r="D114" s="4"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B115">
-        <v>3</v>
-      </c>
-      <c r="C115">
+      <c r="B115" s="4">
+        <v>3</v>
+      </c>
+      <c r="C115" s="4">
         <v>145208</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
+      <c r="D115" s="4"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B116">
-        <v>3</v>
-      </c>
-      <c r="C116">
+      <c r="B116" s="4">
+        <v>3</v>
+      </c>
+      <c r="C116" s="4">
         <v>117764</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
+      <c r="D116" s="4"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B117">
-        <v>3</v>
-      </c>
-      <c r="C117">
+      <c r="B117" s="4">
+        <v>3</v>
+      </c>
+      <c r="C117" s="4">
         <v>220742</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
+      <c r="D117" s="4"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B118">
-        <v>3</v>
-      </c>
-      <c r="C118">
+      <c r="B118" s="4">
+        <v>3</v>
+      </c>
+      <c r="C118" s="4">
         <v>130776</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
+      <c r="D118" s="4"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B119">
-        <v>3</v>
-      </c>
-      <c r="C119">
+      <c r="B119" s="4">
+        <v>3</v>
+      </c>
+      <c r="C119" s="4">
         <v>168561</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
+      <c r="D119" s="4"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B120">
-        <v>3</v>
-      </c>
-      <c r="C120">
+      <c r="B120" s="4">
+        <v>3</v>
+      </c>
+      <c r="C120" s="4">
         <v>234965</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
+      <c r="D120" s="4"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B121">
-        <v>3</v>
-      </c>
-      <c r="C121">
+      <c r="B121" s="4">
+        <v>3</v>
+      </c>
+      <c r="C121" s="4">
         <v>170104</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
+      <c r="D121" s="4"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B122">
-        <v>3</v>
-      </c>
-      <c r="C122">
+      <c r="B122" s="4">
+        <v>3</v>
+      </c>
+      <c r="C122" s="4">
         <v>88487</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
+      <c r="D122" s="4"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B123">
-        <v>3</v>
-      </c>
-      <c r="C123">
+      <c r="B123" s="4">
+        <v>3</v>
+      </c>
+      <c r="C123" s="4">
         <v>61344</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
+      <c r="D123" s="4"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B124">
-        <v>3</v>
-      </c>
-      <c r="C124">
+      <c r="B124" s="4">
+        <v>3</v>
+      </c>
+      <c r="C124" s="4">
         <v>140530</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
+      <c r="D124" s="4"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B125">
-        <v>3</v>
-      </c>
-      <c r="C125">
+      <c r="B125" s="4">
+        <v>3</v>
+      </c>
+      <c r="C125" s="4">
         <v>292534</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
+      <c r="D125" s="4"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B126">
-        <v>3</v>
-      </c>
-      <c r="C126">
+      <c r="B126" s="4">
+        <v>3</v>
+      </c>
+      <c r="C126" s="4">
         <v>206569</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
+      <c r="D126" s="4"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B127">
-        <v>3</v>
-      </c>
-      <c r="C127">
+      <c r="B127" s="4">
+        <v>3</v>
+      </c>
+      <c r="C127" s="4">
         <v>118452</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
+      <c r="D127" s="4"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B128">
-        <v>3</v>
-      </c>
-      <c r="C128">
+      <c r="B128" s="4">
+        <v>3</v>
+      </c>
+      <c r="C128" s="4">
         <v>205242</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
+      <c r="D128" s="4"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B129">
-        <v>3</v>
-      </c>
-      <c r="C129">
+      <c r="B129" s="4">
+        <v>3</v>
+      </c>
+      <c r="C129" s="4">
         <v>228684</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
+      <c r="D129" s="4"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B130">
-        <v>3</v>
-      </c>
-      <c r="C130">
+      <c r="B130" s="4">
+        <v>3</v>
+      </c>
+      <c r="C130" s="4">
         <v>133925</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
+      <c r="D130" s="4"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B131">
-        <v>3</v>
-      </c>
-      <c r="C131">
+      <c r="B131" s="4">
+        <v>3</v>
+      </c>
+      <c r="C131" s="4">
         <v>99568</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
+      <c r="D131" s="4"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B132">
-        <v>3</v>
-      </c>
-      <c r="C132">
+      <c r="B132" s="4">
+        <v>3</v>
+      </c>
+      <c r="C132" s="4">
         <v>83619</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
+      <c r="D132" s="4"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B133">
-        <v>3</v>
-      </c>
-      <c r="C133">
+      <c r="B133" s="4">
+        <v>3</v>
+      </c>
+      <c r="C133" s="4">
         <v>159473</v>
       </c>
+      <c r="D133" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D133" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="GU_019"/>
-        <filter val="IU_019"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2140,12 +2279,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="9.68359375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -2156,7 +2295,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -2167,7 +2306,7 @@
         <v>288751</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -2178,7 +2317,7 @@
         <v>300410</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2189,7 +2328,7 @@
         <v>379812</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -2200,7 +2339,7 @@
         <v>345954</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -2211,7 +2350,7 @@
         <v>285770</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -2222,7 +2361,7 @@
         <v>246189</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2233,7 +2372,7 @@
         <v>351330</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -2244,7 +2383,7 @@
         <v>360742</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -2255,7 +2394,7 @@
         <v>72689</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -2266,7 +2405,7 @@
         <v>143989</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -2277,7 +2416,7 @@
         <v>335545</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -2288,7 +2427,7 @@
         <v>289691</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -2299,7 +2438,7 @@
         <v>390059</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -2310,7 +2449,7 @@
         <v>215774</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -2321,7 +2460,7 @@
         <v>99080</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -2332,7 +2471,7 @@
         <v>52532</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -2343,7 +2482,7 @@
         <v>305267</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -2354,7 +2493,7 @@
         <v>229295</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -2365,7 +2504,7 @@
         <v>237689</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -2376,7 +2515,7 @@
         <v>102218</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -2387,7 +2526,7 @@
         <v>163213</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -2398,7 +2537,7 @@
         <v>94152</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -2409,7 +2548,7 @@
         <v>206278</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -2420,7 +2559,7 @@
         <v>68197</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2431,7 +2570,7 @@
         <v>261977</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -2442,7 +2581,7 @@
         <v>297319</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -2453,7 +2592,7 @@
         <v>290623</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -2464,7 +2603,7 @@
         <v>233772</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -2475,7 +2614,7 @@
         <v>122143</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -2486,7 +2625,7 @@
         <v>70257</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -2497,7 +2636,7 @@
         <v>312051</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -2508,7 +2647,7 @@
         <v>125440</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -2519,7 +2658,7 @@
         <v>39255</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>23</v>
       </c>
@@ -2530,7 +2669,7 @@
         <v>242965</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -2541,7 +2680,7 @@
         <v>122528</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -2552,7 +2691,7 @@
         <v>126238</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -2563,7 +2702,7 @@
         <v>48377</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>34</v>
       </c>
@@ -2574,7 +2713,7 @@
         <v>321647</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -2585,7 +2724,7 @@
         <v>191490</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -2596,7 +2735,7 @@
         <v>274319</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>27</v>
       </c>
@@ -2607,7 +2746,7 @@
         <v>244219</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>29</v>
       </c>
@@ -2618,7 +2757,7 @@
         <v>118326</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -2629,7 +2768,7 @@
         <v>396025</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>39</v>
       </c>
@@ -2640,7 +2779,7 @@
         <v>357371</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>33</v>
       </c>
@@ -2651,7 +2790,7 @@
         <v>366841</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -2662,7 +2801,7 @@
         <v>193786</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -2673,7 +2812,7 @@
         <v>339945</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>41</v>
       </c>
@@ -2684,7 +2823,7 @@
         <v>342152</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -2695,7 +2834,7 @@
         <v>359855</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>26</v>
       </c>
@@ -2706,7 +2845,7 @@
         <v>54818</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -2717,7 +2856,7 @@
         <v>295856</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>32</v>
       </c>
@@ -2728,7 +2867,7 @@
         <v>333891</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>24</v>
       </c>
@@ -2739,7 +2878,7 @@
         <v>259374</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>23</v>
       </c>
@@ -2750,7 +2889,7 @@
         <v>360479</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>31</v>
       </c>
@@ -2761,7 +2900,7 @@
         <v>239190</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>42</v>
       </c>
@@ -2772,7 +2911,7 @@
         <v>172450</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>40</v>
       </c>
@@ -2783,7 +2922,7 @@
         <v>87541</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>34</v>
       </c>
@@ -2794,7 +2933,7 @@
         <v>334879</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>46</v>
       </c>
@@ -2805,7 +2944,7 @@
         <v>297923</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>47</v>
       </c>
@@ -2824,12 +2963,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.29296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -2840,7 +2979,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -2851,7 +2990,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -2862,7 +3001,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -2873,7 +3012,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2884,7 +3023,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -2895,7 +3034,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -2906,7 +3045,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -2917,7 +3056,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -2928,7 +3067,7 @@
         <v>2086</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -2939,7 +3078,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -2950,7 +3089,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -2961,7 +3100,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -2972,7 +3111,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -2983,7 +3122,7 @@
         <v>2119</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2994,7 +3133,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -3005,7 +3144,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -3016,7 +3155,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -3027,7 +3166,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -3038,7 +3177,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -3049,7 +3188,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -3060,7 +3199,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -3071,7 +3210,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -3082,7 +3221,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -3093,7 +3232,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -3104,7 +3243,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -3115,7 +3254,7 @@
         <v>1668</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -3126,7 +3265,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -3137,7 +3276,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -3148,7 +3287,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -3159,7 +3298,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -3170,7 +3309,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -3181,7 +3320,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -3192,7 +3331,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -3203,7 +3342,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -3214,7 +3353,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -3225,7 +3364,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -3236,7 +3375,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -3247,7 +3386,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -3258,7 +3397,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -3269,7 +3408,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>47</v>
       </c>
@@ -3280,7 +3419,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -3291,7 +3430,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>33</v>
       </c>
@@ -3302,7 +3441,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -3313,7 +3452,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -3324,7 +3463,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>32</v>
       </c>
@@ -3335,7 +3474,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -3346,7 +3485,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -3357,7 +3496,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>23</v>
       </c>
@@ -3368,7 +3507,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -3379,7 +3518,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -3390,7 +3529,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>26</v>
       </c>
@@ -3401,7 +3540,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -3412,7 +3551,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>29</v>
       </c>
@@ -3423,7 +3562,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>31</v>
       </c>
@@ -3434,7 +3573,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>39</v>
       </c>
@@ -3445,7 +3584,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>40</v>
       </c>
@@ -3456,7 +3595,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>41</v>
       </c>
@@ -3467,7 +3606,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>42</v>
       </c>
@@ -3478,7 +3617,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>46</v>
       </c>
@@ -3489,7 +3628,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>47</v>
       </c>
@@ -3507,20 +3646,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G349"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.2578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.94921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5859375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.73828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.5234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -3543,7 +3681,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -3566,7 +3704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -3589,7 +3727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -3612,7 +3750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -3635,7 +3773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -3658,7 +3796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -3681,7 +3819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -3704,7 +3842,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -3727,7 +3865,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -3750,7 +3888,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -3773,7 +3911,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -3796,7 +3934,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -3819,7 +3957,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -3842,7 +3980,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -3865,7 +4003,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -3888,7 +4026,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -3911,7 +4049,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -3934,7 +4072,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -3957,7 +4095,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -3980,7 +4118,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -4003,7 +4141,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -4026,7 +4164,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -4049,7 +4187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -4072,7 +4210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -4095,7 +4233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -4118,7 +4256,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -4141,7 +4279,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -4164,7 +4302,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -4187,7 +4325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -4210,7 +4348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -4233,7 +4371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -4256,7 +4394,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -4279,7 +4417,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -4302,7 +4440,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -4325,7 +4463,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -4348,7 +4486,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -4371,7 +4509,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -4394,7 +4532,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -4417,7 +4555,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -4440,7 +4578,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -4463,7 +4601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -4486,7 +4624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>39</v>
       </c>
@@ -4509,7 +4647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>39</v>
       </c>
@@ -4532,7 +4670,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>39</v>
       </c>
@@ -4555,7 +4693,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -4578,7 +4716,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -4601,7 +4739,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -4624,7 +4762,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -4647,7 +4785,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>39</v>
       </c>
@@ -4670,7 +4808,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -4693,7 +4831,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>39</v>
       </c>
@@ -4716,7 +4854,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -4739,7 +4877,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>39</v>
       </c>
@@ -4762,7 +4900,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>39</v>
       </c>
@@ -4785,7 +4923,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>39</v>
       </c>
@@ -4808,7 +4946,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>39</v>
       </c>
@@ -4831,7 +4969,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>39</v>
       </c>
@@ -4854,7 +4992,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>33</v>
       </c>
@@ -4877,7 +5015,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>33</v>
       </c>
@@ -4900,7 +5038,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>33</v>
       </c>
@@ -4923,7 +5061,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>33</v>
       </c>
@@ -4946,7 +5084,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>33</v>
       </c>
@@ -4969,7 +5107,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>33</v>
       </c>
@@ -4992,7 +5130,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>33</v>
       </c>
@@ -5015,7 +5153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>33</v>
       </c>
@@ -5038,7 +5176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>33</v>
       </c>
@@ -5061,7 +5199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>33</v>
       </c>
@@ -5084,7 +5222,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>33</v>
       </c>
@@ -5107,7 +5245,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>33</v>
       </c>
@@ -5130,7 +5268,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>33</v>
       </c>
@@ -5153,7 +5291,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>33</v>
       </c>
@@ -5176,7 +5314,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>33</v>
       </c>
@@ -5199,7 +5337,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>33</v>
       </c>
@@ -5222,7 +5360,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>33</v>
       </c>
@@ -5245,7 +5383,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>33</v>
       </c>
@@ -5268,7 +5406,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>33</v>
       </c>
@@ -5291,7 +5429,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>33</v>
       </c>
@@ -5314,7 +5452,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>33</v>
       </c>
@@ -5337,7 +5475,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>33</v>
       </c>
@@ -5360,7 +5498,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>33</v>
       </c>
@@ -5383,7 +5521,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>33</v>
       </c>
@@ -5406,7 +5544,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>33</v>
       </c>
@@ -5429,7 +5567,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>33</v>
       </c>
@@ -5452,7 +5590,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>33</v>
       </c>
@@ -5475,7 +5613,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>47</v>
       </c>
@@ -5498,7 +5636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>47</v>
       </c>
@@ -5521,7 +5659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>47</v>
       </c>
@@ -5544,7 +5682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>47</v>
       </c>
@@ -5567,7 +5705,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>47</v>
       </c>
@@ -5590,7 +5728,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>47</v>
       </c>
@@ -5613,7 +5751,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>47</v>
       </c>
@@ -5636,7 +5774,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>47</v>
       </c>
@@ -5659,7 +5797,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>47</v>
       </c>
@@ -5682,7 +5820,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>47</v>
       </c>
@@ -5705,7 +5843,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>47</v>
       </c>
@@ -5728,7 +5866,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>47</v>
       </c>
@@ -5751,7 +5889,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>47</v>
       </c>
@@ -5774,7 +5912,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>47</v>
       </c>
@@ -5797,7 +5935,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>47</v>
       </c>
@@ -5820,7 +5958,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>13</v>
       </c>
@@ -5843,7 +5981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>13</v>
       </c>
@@ -5866,7 +6004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>13</v>
       </c>
@@ -5889,7 +6027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>13</v>
       </c>
@@ -5912,7 +6050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>13</v>
       </c>
@@ -5935,7 +6073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>13</v>
       </c>
@@ -5958,7 +6096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>13</v>
       </c>
@@ -5981,7 +6119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>13</v>
       </c>
@@ -6004,7 +6142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>13</v>
       </c>
@@ -6027,7 +6165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>13</v>
       </c>
@@ -6050,7 +6188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>13</v>
       </c>
@@ -6073,7 +6211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>13</v>
       </c>
@@ -6096,7 +6234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>13</v>
       </c>
@@ -6119,7 +6257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>13</v>
       </c>
@@ -6142,7 +6280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>13</v>
       </c>
@@ -6165,7 +6303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>46</v>
       </c>
@@ -6188,7 +6326,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>46</v>
       </c>
@@ -6211,7 +6349,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>46</v>
       </c>
@@ -6234,7 +6372,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>46</v>
       </c>
@@ -6257,7 +6395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>46</v>
       </c>
@@ -6280,7 +6418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>46</v>
       </c>
@@ -6303,7 +6441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>46</v>
       </c>
@@ -6326,7 +6464,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>46</v>
       </c>
@@ -6349,7 +6487,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>46</v>
       </c>
@@ -6372,7 +6510,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>46</v>
       </c>
@@ -6395,7 +6533,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>46</v>
       </c>
@@ -6418,7 +6556,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>46</v>
       </c>
@@ -6441,7 +6579,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>46</v>
       </c>
@@ -6464,7 +6602,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>46</v>
       </c>
@@ -6487,7 +6625,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>46</v>
       </c>
@@ -6510,7 +6648,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>46</v>
       </c>
@@ -6533,7 +6671,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>46</v>
       </c>
@@ -6556,7 +6694,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>46</v>
       </c>
@@ -6579,7 +6717,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>46</v>
       </c>
@@ -6602,7 +6740,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>46</v>
       </c>
@@ -6625,7 +6763,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>46</v>
       </c>
@@ -6648,7 +6786,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>14</v>
       </c>
@@ -6671,7 +6809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>14</v>
       </c>
@@ -6694,7 +6832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>14</v>
       </c>
@@ -6717,7 +6855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>14</v>
       </c>
@@ -6740,7 +6878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>14</v>
       </c>
@@ -6763,7 +6901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>14</v>
       </c>
@@ -6786,7 +6924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>14</v>
       </c>
@@ -6809,7 +6947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>14</v>
       </c>
@@ -6832,7 +6970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>14</v>
       </c>
@@ -6855,7 +6993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>14</v>
       </c>
@@ -6878,7 +7016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>14</v>
       </c>
@@ -6901,7 +7039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>14</v>
       </c>
@@ -6924,7 +7062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>14</v>
       </c>
@@ -6947,7 +7085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>14</v>
       </c>
@@ -6970,7 +7108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>14</v>
       </c>
@@ -6993,7 +7131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>41</v>
       </c>
@@ -7016,7 +7154,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>41</v>
       </c>
@@ -7039,7 +7177,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>41</v>
       </c>
@@ -7062,7 +7200,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>41</v>
       </c>
@@ -7085,7 +7223,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>41</v>
       </c>
@@ -7108,7 +7246,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>41</v>
       </c>
@@ -7131,7 +7269,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>41</v>
       </c>
@@ -7154,7 +7292,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>41</v>
       </c>
@@ -7177,7 +7315,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>41</v>
       </c>
@@ -7200,7 +7338,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>41</v>
       </c>
@@ -7223,7 +7361,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>41</v>
       </c>
@@ -7246,7 +7384,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>41</v>
       </c>
@@ -7269,7 +7407,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>41</v>
       </c>
@@ -7292,7 +7430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>41</v>
       </c>
@@ -7315,7 +7453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>41</v>
       </c>
@@ -7338,7 +7476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>41</v>
       </c>
@@ -7361,7 +7499,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>41</v>
       </c>
@@ -7384,7 +7522,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>41</v>
       </c>
@@ -7407,7 +7545,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>41</v>
       </c>
@@ -7430,7 +7568,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>41</v>
       </c>
@@ -7453,7 +7591,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>41</v>
       </c>
@@ -7476,7 +7614,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>41</v>
       </c>
@@ -7499,7 +7637,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>41</v>
       </c>
@@ -7522,7 +7660,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>41</v>
       </c>
@@ -7545,7 +7683,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>41</v>
       </c>
@@ -7568,7 +7706,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>41</v>
       </c>
@@ -7591,7 +7729,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>41</v>
       </c>
@@ -7614,7 +7752,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>41</v>
       </c>
@@ -7637,7 +7775,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>41</v>
       </c>
@@ -7660,7 +7798,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>41</v>
       </c>
@@ -7683,7 +7821,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>41</v>
       </c>
@@ -7706,7 +7844,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>41</v>
       </c>
@@ -7729,7 +7867,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>41</v>
       </c>
@@ -7752,7 +7890,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>41</v>
       </c>
@@ -7775,7 +7913,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>41</v>
       </c>
@@ -7798,7 +7936,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>41</v>
       </c>
@@ -7821,7 +7959,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>5</v>
       </c>
@@ -7844,7 +7982,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>5</v>
       </c>
@@ -7867,7 +8005,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>5</v>
       </c>
@@ -7890,7 +8028,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>5</v>
       </c>
@@ -7913,7 +8051,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>5</v>
       </c>
@@ -7936,7 +8074,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>5</v>
       </c>
@@ -7959,7 +8097,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>5</v>
       </c>
@@ -7982,7 +8120,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>5</v>
       </c>
@@ -8005,7 +8143,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>5</v>
       </c>
@@ -8028,7 +8166,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>5</v>
       </c>
@@ -8051,7 +8189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>5</v>
       </c>
@@ -8074,7 +8212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>5</v>
       </c>
@@ -8097,7 +8235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>5</v>
       </c>
@@ -8120,7 +8258,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>5</v>
       </c>
@@ -8143,7 +8281,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>5</v>
       </c>
@@ -8166,7 +8304,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>60</v>
       </c>
@@ -8189,7 +8327,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>60</v>
       </c>
@@ -8212,7 +8350,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>60</v>
       </c>
@@ -8235,7 +8373,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>61</v>
       </c>
@@ -8258,7 +8396,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>61</v>
       </c>
@@ -8281,7 +8419,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>61</v>
       </c>
@@ -8304,7 +8442,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>26</v>
       </c>
@@ -8327,7 +8465,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>26</v>
       </c>
@@ -8350,7 +8488,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>26</v>
       </c>
@@ -8373,7 +8511,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>26</v>
       </c>
@@ -8396,7 +8534,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>26</v>
       </c>
@@ -8419,7 +8557,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>26</v>
       </c>
@@ -8442,7 +8580,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>26</v>
       </c>
@@ -8465,7 +8603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>26</v>
       </c>
@@ -8488,7 +8626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>26</v>
       </c>
@@ -8511,7 +8649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>26</v>
       </c>
@@ -8534,7 +8672,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>26</v>
       </c>
@@ -8557,7 +8695,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>26</v>
       </c>
@@ -8580,7 +8718,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>26</v>
       </c>
@@ -8603,7 +8741,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>26</v>
       </c>
@@ -8626,7 +8764,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>26</v>
       </c>
@@ -8649,7 +8787,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>26</v>
       </c>
@@ -8672,7 +8810,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>26</v>
       </c>
@@ -8695,7 +8833,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>26</v>
       </c>
@@ -8718,7 +8856,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>25</v>
       </c>
@@ -8741,7 +8879,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>25</v>
       </c>
@@ -8764,7 +8902,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>25</v>
       </c>
@@ -8787,7 +8925,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>25</v>
       </c>
@@ -8810,7 +8948,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>25</v>
       </c>
@@ -8833,7 +8971,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>25</v>
       </c>
@@ -8856,7 +8994,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>25</v>
       </c>
@@ -8879,7 +9017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>25</v>
       </c>
@@ -8902,7 +9040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>25</v>
       </c>
@@ -8925,7 +9063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>25</v>
       </c>
@@ -8948,7 +9086,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>25</v>
       </c>
@@ -8971,7 +9109,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>25</v>
       </c>
@@ -8994,7 +9132,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>25</v>
       </c>
@@ -9017,7 +9155,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>25</v>
       </c>
@@ -9040,7 +9178,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>25</v>
       </c>
@@ -9063,7 +9201,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>25</v>
       </c>
@@ -9086,7 +9224,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>25</v>
       </c>
@@ -9109,7 +9247,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>25</v>
       </c>
@@ -9132,7 +9270,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>32</v>
       </c>
@@ -9155,7 +9293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>32</v>
       </c>
@@ -9178,7 +9316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>32</v>
       </c>
@@ -9201,7 +9339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>24</v>
       </c>
@@ -9224,7 +9362,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>24</v>
       </c>
@@ -9247,7 +9385,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>24</v>
       </c>
@@ -9270,7 +9408,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>24</v>
       </c>
@@ -9293,7 +9431,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>24</v>
       </c>
@@ -9316,7 +9454,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>24</v>
       </c>
@@ -9339,7 +9477,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>24</v>
       </c>
@@ -9362,7 +9500,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>24</v>
       </c>
@@ -9385,7 +9523,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>24</v>
       </c>
@@ -9408,7 +9546,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>24</v>
       </c>
@@ -9431,7 +9569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>24</v>
       </c>
@@ -9454,7 +9592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>24</v>
       </c>
@@ -9477,7 +9615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>24</v>
       </c>
@@ -9500,7 +9638,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>24</v>
       </c>
@@ -9523,7 +9661,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>24</v>
       </c>
@@ -9546,7 +9684,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="263" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>24</v>
       </c>
@@ -9569,7 +9707,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="264" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>24</v>
       </c>
@@ -9592,7 +9730,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>24</v>
       </c>
@@ -9615,7 +9753,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>24</v>
       </c>
@@ -9638,7 +9776,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>24</v>
       </c>
@@ -9661,7 +9799,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>24</v>
       </c>
@@ -9684,7 +9822,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>23</v>
       </c>
@@ -9707,7 +9845,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>23</v>
       </c>
@@ -9730,7 +9868,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>23</v>
       </c>
@@ -9753,7 +9891,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>23</v>
       </c>
@@ -9776,7 +9914,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>23</v>
       </c>
@@ -9799,7 +9937,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>23</v>
       </c>
@@ -9822,7 +9960,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>23</v>
       </c>
@@ -9845,7 +9983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>23</v>
       </c>
@@ -9868,7 +10006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>23</v>
       </c>
@@ -9891,7 +10029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>23</v>
       </c>
@@ -9914,7 +10052,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>23</v>
       </c>
@@ -9937,7 +10075,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>23</v>
       </c>
@@ -9960,7 +10098,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>31</v>
       </c>
@@ -9983,7 +10121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>31</v>
       </c>
@@ -10006,7 +10144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>31</v>
       </c>
@@ -10029,7 +10167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>31</v>
       </c>
@@ -10052,7 +10190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>31</v>
       </c>
@@ -10075,7 +10213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>31</v>
       </c>
@@ -10098,7 +10236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>31</v>
       </c>
@@ -10121,7 +10259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>31</v>
       </c>
@@ -10144,7 +10282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>31</v>
       </c>
@@ -10167,7 +10305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>42</v>
       </c>
@@ -10190,7 +10328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>42</v>
       </c>
@@ -10213,7 +10351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>42</v>
       </c>
@@ -10236,7 +10374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>42</v>
       </c>
@@ -10259,7 +10397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>42</v>
       </c>
@@ -10282,7 +10420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>42</v>
       </c>
@@ -10305,7 +10443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>40</v>
       </c>
@@ -10328,7 +10466,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>40</v>
       </c>
@@ -10351,7 +10489,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>40</v>
       </c>
@@ -10374,7 +10512,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>40</v>
       </c>
@@ -10397,7 +10535,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>40</v>
       </c>
@@ -10420,7 +10558,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>40</v>
       </c>
@@ -10443,7 +10581,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>40</v>
       </c>
@@ -10466,7 +10604,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>40</v>
       </c>
@@ -10489,7 +10627,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>40</v>
       </c>
@@ -10512,7 +10650,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>40</v>
       </c>
@@ -10535,7 +10673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>40</v>
       </c>
@@ -10558,7 +10696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>40</v>
       </c>
@@ -10581,7 +10719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>40</v>
       </c>
@@ -10604,7 +10742,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>40</v>
       </c>
@@ -10627,7 +10765,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>40</v>
       </c>
@@ -10650,7 +10788,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="311" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>40</v>
       </c>
@@ -10673,7 +10811,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="312" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>40</v>
       </c>
@@ -10696,7 +10834,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>40</v>
       </c>
@@ -10719,7 +10857,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="314" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>34</v>
       </c>
@@ -10742,7 +10880,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="315" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>34</v>
       </c>
@@ -10765,7 +10903,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="316" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>34</v>
       </c>
@@ -10788,7 +10926,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="317" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>34</v>
       </c>
@@ -10811,7 +10949,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="318" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>34</v>
       </c>
@@ -10834,7 +10972,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="319" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>34</v>
       </c>
@@ -10857,7 +10995,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="320" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>34</v>
       </c>
@@ -10880,7 +11018,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>34</v>
       </c>
@@ -10903,7 +11041,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>34</v>
       </c>
@@ -10926,7 +11064,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>34</v>
       </c>
@@ -10949,7 +11087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>34</v>
       </c>
@@ -10972,7 +11110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>34</v>
       </c>
@@ -10995,7 +11133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>34</v>
       </c>
@@ -11018,7 +11156,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>34</v>
       </c>
@@ -11041,7 +11179,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>34</v>
       </c>
@@ -11064,7 +11202,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>63</v>
       </c>
@@ -11087,7 +11225,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>63</v>
       </c>
@@ -11110,7 +11248,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>63</v>
       </c>
@@ -11133,7 +11271,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>13</v>
       </c>
@@ -11156,7 +11294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>13</v>
       </c>
@@ -11179,7 +11317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>13</v>
       </c>
@@ -11202,7 +11340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>13</v>
       </c>
@@ -11225,7 +11363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>13</v>
       </c>
@@ -11248,7 +11386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>13</v>
       </c>
@@ -11271,7 +11409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>24</v>
       </c>
@@ -11294,7 +11432,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>24</v>
       </c>
@@ -11317,7 +11455,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>24</v>
       </c>
@@ -11340,7 +11478,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>5</v>
       </c>
@@ -11363,7 +11501,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>5</v>
       </c>
@@ -11386,7 +11524,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>5</v>
       </c>
@@ -11409,7 +11547,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>5</v>
       </c>
@@ -11432,7 +11570,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>5</v>
       </c>
@@ -11455,7 +11593,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>5</v>
       </c>
@@ -11478,7 +11616,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>39</v>
       </c>
@@ -11501,7 +11639,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>39</v>
       </c>
@@ -11524,7 +11662,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>39</v>
       </c>
@@ -11548,13 +11686,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G349" xr:uid="{00000000-0001-0000-0300-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="GU_019"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11562,18 +11693,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G76"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.33984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.94921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.390625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5859375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.609375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -11596,7 +11727,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -11616,7 +11747,7 @@
         <v>233200</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -11636,7 +11767,7 @@
         <v>176000</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -11656,7 +11787,7 @@
         <v>252999.99999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -11676,7 +11807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -11693,7 +11824,7 @@
         <v>196000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -11713,7 +11844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -11730,7 +11861,7 @@
         <v>178000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -11750,7 +11881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -11767,7 +11898,7 @@
         <v>172000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -11787,7 +11918,7 @@
         <v>112320</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -11807,7 +11938,7 @@
         <v>147264</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -11827,7 +11958,7 @@
         <v>147264</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -11850,7 +11981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -11873,7 +12004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -11896,7 +12027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -11916,7 +12047,7 @@
         <v>10815</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -11933,7 +12064,7 @@
         <v>503100</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -11953,7 +12084,7 @@
         <v>8610</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -11970,7 +12101,7 @@
         <v>464100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -11990,7 +12121,7 @@
         <v>12915</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -12007,7 +12138,7 @@
         <v>436800.00000000006</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -12027,7 +12158,7 @@
         <v>51500</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -12047,7 +12178,7 @@
         <v>43500</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -12067,7 +12198,7 @@
         <v>4450</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -12090,7 +12221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -12107,7 +12238,7 @@
         <v>156420</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -12130,7 +12261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -12147,7 +12278,7 @@
         <v>175972.5</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -12170,7 +12301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -12187,7 +12318,7 @@
         <v>209745</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -12204,7 +12335,7 @@
         <v>110400</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -12221,7 +12352,7 @@
         <v>108000</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>14</v>
       </c>
@@ -12238,7 +12369,7 @@
         <v>127200</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>41</v>
       </c>
@@ -12258,7 +12389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -12278,7 +12409,7 @@
         <v>47040</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -12298,7 +12429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -12318,7 +12449,7 @@
         <v>42240</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -12338,7 +12469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -12358,7 +12489,7 @@
         <v>49920</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -12378,7 +12509,7 @@
         <v>211200</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -12398,7 +12529,7 @@
         <v>246400.00000000003</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -12418,7 +12549,7 @@
         <v>226600</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>26</v>
       </c>
@@ -12438,7 +12569,7 @@
         <v>198000.00000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>26</v>
       </c>
@@ -12458,7 +12589,7 @@
         <v>172800</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -12478,7 +12609,7 @@
         <v>221400</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -12498,7 +12629,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>25</v>
       </c>
@@ -12518,7 +12649,7 @@
         <v>15200</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -12538,7 +12669,7 @@
         <v>15520</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -12555,7 +12686,7 @@
         <v>68860</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -12575,7 +12706,7 @@
         <v>19200</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -12595,7 +12726,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -12615,7 +12746,7 @@
         <v>18720</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -12632,7 +12763,7 @@
         <v>62600</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -12652,7 +12783,7 @@
         <v>13600</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -12672,7 +12803,7 @@
         <v>14560</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -12692,7 +12823,7 @@
         <v>14560</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -12709,7 +12840,7 @@
         <v>60722</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>24</v>
       </c>
@@ -12726,7 +12857,7 @@
         <v>278400</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>24</v>
       </c>
@@ -12746,7 +12877,7 @@
         <v>44118</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>24</v>
       </c>
@@ -12766,7 +12897,7 @@
         <v>261600.00000000003</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>24</v>
       </c>
@@ -12783,7 +12914,7 @@
         <v>196800</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>24</v>
       </c>
@@ -12803,7 +12934,7 @@
         <v>33174</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>24</v>
       </c>
@@ -12823,7 +12954,7 @@
         <v>304800</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>24</v>
       </c>
@@ -12840,7 +12971,7 @@
         <v>266400</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>24</v>
       </c>
@@ -12860,7 +12991,7 @@
         <v>41382</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>24</v>
       </c>
@@ -12880,7 +13011,7 @@
         <v>266400</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>24</v>
       </c>
@@ -12900,7 +13031,7 @@
         <v>45900</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>24</v>
       </c>
@@ -12920,7 +13051,7 @@
         <v>58050</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>24</v>
       </c>
@@ -12940,7 +13071,7 @@
         <v>39100</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>23</v>
       </c>
@@ -12960,7 +13091,7 @@
         <v>45540</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>23</v>
       </c>
@@ -12980,7 +13111,7 @@
         <v>46920</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>23</v>
       </c>
@@ -13000,7 +13131,7 @@
         <v>38640</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>40</v>
       </c>
@@ -13020,7 +13151,7 @@
         <v>48600</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>40</v>
       </c>
@@ -13040,7 +13171,7 @@
         <v>57600</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>40</v>
       </c>
@@ -13068,13 +13199,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.73828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13082,7 +13213,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -13090,7 +13221,7 @@
         <v>14533.462029913042</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -13098,7 +13229,7 @@
         <v>85529.681327086349</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -13106,7 +13237,7 @@
         <v>2959.0305099999982</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -13114,7 +13245,7 @@
         <v>28224.812272178173</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -13122,7 +13253,7 @@
         <v>15677.025000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -13130,7 +13261,7 @@
         <v>3898.9300000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -13138,7 +13269,7 @@
         <v>19551.361677436103</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -13146,7 +13277,7 @@
         <v>773.11793658464728</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -13154,7 +13285,7 @@
         <v>6763.6828869501569</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -13162,7 +13293,7 @@
         <v>56975.149634648616</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -13170,7 +13301,7 @@
         <v>10895.393495717344</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -13178,7 +13309,7 @@
         <v>21855.908904558873</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -13186,7 +13317,7 @@
         <v>11189.388964096461</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -13194,7 +13325,7 @@
         <v>81492.081907951404</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -13202,7 +13333,7 @@
         <v>15255.838656542357</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -13210,7 +13341,7 @@
         <v>15558.806053056989</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -13218,7 +13349,7 @@
         <v>14018.27198334389</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -13226,7 +13357,7 @@
         <v>17204.337891567415</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -13234,7 +13365,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -13242,7 +13373,7 @@
         <v>4205.5214590111555</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -13250,7 +13381,7 @@
         <v>9926.1773426677319</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -13258,7 +13389,7 @@
         <v>19310.984000000029</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -13266,7 +13397,7 @@
         <v>40427</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -13274,7 +13405,7 @@
         <v>2952.4218850746288</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -13282,7 +13413,7 @@
         <v>87177.269662466671</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -13290,7 +13421,7 @@
         <v>127537.21</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -13298,7 +13429,7 @@
         <v>8197.0331591752256</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -13306,7 +13437,7 @@
         <v>4628.3550000000032</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -13314,7 +13445,7 @@
         <v>55667.654093014593</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>22</v>
       </c>
@@ -13322,7 +13453,7 @@
         <v>9693.2289999999921</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -13330,7 +13461,7 @@
         <v>14614.400000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -13338,7 +13469,7 @@
         <v>89718.225747316421</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -13346,7 +13477,7 @@
         <v>176793.49860933746</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -13354,7 +13485,7 @@
         <v>50164.305214624525</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -13362,7 +13493,7 @@
         <v>45075.079780374654</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -13370,7 +13501,7 @@
         <v>5376.1259690153192</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -13378,7 +13509,7 @@
         <v>7651.4941163323483</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>35</v>
       </c>
@@ -13386,7 +13517,7 @@
         <v>3962.8353638316762</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>28</v>
       </c>
@@ -13394,7 +13525,7 @@
         <v>41196.32160000001</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -13402,7 +13533,7 @@
         <v>2763.8262597469038</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -13410,7 +13541,7 @@
         <v>31958.733383719493</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -13418,7 +13549,7 @@
         <v>36494.008886004616</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -13426,7 +13557,7 @@
         <v>24846.888832319066</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -13442,9 +13573,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>72</v>
       </c>
@@ -13455,7 +13586,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -13466,7 +13597,7 @@
         <v>77343.298058031403</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -13477,7 +13608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -13496,13 +13627,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D133"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.94921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.62109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13516,7 +13649,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -13530,7 +13663,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -13544,7 +13677,7 @@
         <v>352000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -13555,7 +13688,7 @@
         <v>14100</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -13566,7 +13699,7 @@
         <v>39300</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -13577,7 +13710,7 @@
         <v>14400</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -13588,7 +13721,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -13602,7 +13735,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -13616,7 +13749,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -13627,7 +13760,7 @@
         <v>25200</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -13641,7 +13774,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -13652,7 +13785,7 @@
         <v>29800</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>30</v>
       </c>
@@ -13663,7 +13796,7 @@
         <v>53600</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -13674,7 +13807,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -13688,7 +13821,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -13699,7 +13832,7 @@
         <v>21400</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -13713,7 +13846,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>41</v>
       </c>
@@ -13727,7 +13860,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -13741,7 +13874,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -13752,7 +13885,7 @@
         <v>7600</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -13763,7 +13896,7 @@
         <v>12750</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -13774,7 +13907,7 @@
         <v>32750</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -13788,7 +13921,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -13802,7 +13935,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -13813,7 +13946,7 @@
         <v>13050</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -13827,7 +13960,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -13841,7 +13974,7 @@
         <v>113000</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -13852,7 +13985,7 @@
         <v>13500</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>44</v>
       </c>
@@ -13863,7 +13996,7 @@
         <v>16920</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -13877,7 +14010,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>22</v>
       </c>
@@ -13888,7 +14021,7 @@
         <v>13350</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -13899,7 +14032,7 @@
         <v>23800</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -13910,7 +14043,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -13924,7 +14057,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -13935,7 +14068,7 @@
         <v>30800</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -13946,7 +14079,7 @@
         <v>42000</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -13960,7 +14093,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -13974,7 +14107,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>35</v>
       </c>
@@ -13985,7 +14118,7 @@
         <v>64500</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>28</v>
       </c>
@@ -13996,7 +14129,7 @@
         <v>67500</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -14007,7 +14140,7 @@
         <v>11200.000000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -14021,7 +14154,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -14035,7 +14168,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -14049,7 +14182,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -14063,7 +14196,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>27</v>
       </c>
@@ -14077,7 +14210,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>29</v>
       </c>
@@ -14091,7 +14224,7 @@
         <v>352000</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -14102,7 +14235,7 @@
         <v>9700</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -14113,7 +14246,7 @@
         <v>32400.000000000004</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -14124,7 +14257,7 @@
         <v>9200</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>12</v>
       </c>
@@ -14135,7 +14268,7 @@
         <v>10700</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -14149,7 +14282,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -14163,7 +14296,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -14174,7 +14307,7 @@
         <v>13799.999999999998</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>33</v>
       </c>
@@ -14188,7 +14321,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>19</v>
       </c>
@@ -14199,7 +14332,7 @@
         <v>23600</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>30</v>
       </c>
@@ -14210,7 +14343,7 @@
         <v>27599.999999999996</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -14221,7 +14354,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -14235,7 +14368,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>10</v>
       </c>
@@ -14246,7 +14379,7 @@
         <v>17400</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -14260,7 +14393,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>41</v>
       </c>
@@ -14274,7 +14407,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -14288,7 +14421,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>21</v>
       </c>
@@ -14299,7 +14432,7 @@
         <v>8900</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>43</v>
       </c>
@@ -14310,7 +14443,7 @@
         <v>20750</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>36</v>
       </c>
@@ -14321,7 +14454,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>26</v>
       </c>
@@ -14335,7 +14468,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -14349,7 +14482,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>38</v>
       </c>
@@ -14360,7 +14493,7 @@
         <v>13350</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>32</v>
       </c>
@@ -14374,7 +14507,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>24</v>
       </c>
@@ -14388,7 +14521,7 @@
         <v>113000</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -14399,7 +14532,7 @@
         <v>18150</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>44</v>
       </c>
@@ -14410,7 +14543,7 @@
         <v>6120</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>23</v>
       </c>
@@ -14424,7 +14557,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>22</v>
       </c>
@@ -14435,7 +14568,7 @@
         <v>21150</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>20</v>
       </c>
@@ -14446,7 +14579,7 @@
         <v>19800</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>16</v>
       </c>
@@ -14460,7 +14593,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>31</v>
       </c>
@@ -14474,7 +14607,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>8</v>
       </c>
@@ -14485,7 +14618,7 @@
         <v>36400</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>9</v>
       </c>
@@ -14496,7 +14629,7 @@
         <v>20400</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>42</v>
       </c>
@@ -14510,7 +14643,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>40</v>
       </c>
@@ -14524,7 +14657,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>35</v>
       </c>
@@ -14535,7 +14668,7 @@
         <v>74000</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>28</v>
       </c>
@@ -14546,7 +14679,7 @@
         <v>51500</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>37</v>
       </c>
@@ -14557,7 +14690,7 @@
         <v>18600</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>34</v>
       </c>
@@ -14571,7 +14704,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>46</v>
       </c>
@@ -14585,7 +14718,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>47</v>
       </c>
@@ -14599,7 +14732,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>45</v>
       </c>
@@ -14613,7 +14746,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>27</v>
       </c>
@@ -14627,7 +14760,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>29</v>
       </c>
@@ -14641,7 +14774,7 @@
         <v>352000</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>15</v>
       </c>
@@ -14652,7 +14785,7 @@
         <v>5900</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>6</v>
       </c>
@@ -14663,7 +14796,7 @@
         <v>36300</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -14674,7 +14807,7 @@
         <v>14600</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>12</v>
       </c>
@@ -14685,7 +14818,7 @@
         <v>12500</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -14699,7 +14832,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>39</v>
       </c>
@@ -14713,7 +14846,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -14724,7 +14857,7 @@
         <v>26600</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>33</v>
       </c>
@@ -14738,7 +14871,7 @@
         <v>105000</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>19</v>
       </c>
@@ -14749,7 +14882,7 @@
         <v>19000</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>30</v>
       </c>
@@ -14760,7 +14893,7 @@
         <v>54400.000000000007</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -14771,7 +14904,7 @@
         <v>4750</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>13</v>
       </c>
@@ -14785,7 +14918,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>10</v>
       </c>
@@ -14796,7 +14929,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>14</v>
       </c>
@@ -14810,7 +14943,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>41</v>
       </c>
@@ -14824,7 +14957,7 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>5</v>
       </c>
@@ -14838,7 +14971,7 @@
         <v>65000</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>21</v>
       </c>
@@ -14849,7 +14982,7 @@
         <v>7200</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>43</v>
       </c>
@@ -14860,7 +14993,7 @@
         <v>23250</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>36</v>
       </c>
@@ -14871,7 +15004,7 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>26</v>
       </c>
@@ -14885,7 +15018,7 @@
         <v>55000</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>25</v>
       </c>
@@ -14899,7 +15032,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>38</v>
       </c>
@@ -14910,7 +15043,7 @@
         <v>18600</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>32</v>
       </c>
@@ -14924,7 +15057,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>24</v>
       </c>
@@ -14938,7 +15071,7 @@
         <v>113000</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>17</v>
       </c>
@@ -14949,7 +15082,7 @@
         <v>13650</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>44</v>
       </c>
@@ -14960,7 +15093,7 @@
         <v>14520</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>23</v>
       </c>
@@ -14974,7 +15107,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>22</v>
       </c>
@@ -14985,7 +15118,7 @@
         <v>18150</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>20</v>
       </c>
@@ -14996,7 +15129,7 @@
         <v>11800</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>16</v>
       </c>
@@ -15007,7 +15140,7 @@
         <v>144000</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>31</v>
       </c>
@@ -15021,7 +15154,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>8</v>
       </c>
@@ -15032,7 +15165,7 @@
         <v>34300</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>9</v>
       </c>
@@ -15043,7 +15176,7 @@
         <v>50800</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>42</v>
       </c>
@@ -15057,7 +15190,7 @@
         <v>36000</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>40</v>
       </c>
@@ -15071,7 +15204,7 @@
         <v>48000</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>35</v>
       </c>
@@ -15082,7 +15215,7 @@
         <v>49500</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>28</v>
       </c>
@@ -15093,7 +15226,7 @@
         <v>70500</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>37</v>
       </c>
@@ -15104,7 +15237,7 @@
         <v>13200</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>34</v>
       </c>
@@ -15118,7 +15251,7 @@
         <v>165000</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>46</v>
       </c>
@@ -15132,7 +15265,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>47</v>
       </c>
@@ -15146,7 +15279,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>45</v>
       </c>
@@ -15168,14 +15301,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.43359375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.47265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15186,7 +15319,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -15194,7 +15327,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -15202,7 +15335,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -15210,7 +15343,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -15218,7 +15351,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -15226,7 +15359,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -15234,7 +15367,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -15242,7 +15375,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -15253,7 +15386,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -15261,7 +15394,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -15269,7 +15402,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -15277,7 +15410,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -15285,7 +15418,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -15293,7 +15426,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -15301,7 +15434,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -15309,7 +15442,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -15320,7 +15453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -15328,7 +15461,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -15336,7 +15469,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -15344,7 +15477,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -15352,7 +15485,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>44</v>
       </c>
@@ -15360,7 +15493,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -15368,7 +15501,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -15376,7 +15509,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -15384,7 +15517,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -15392,7 +15525,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -15400,7 +15533,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -15408,7 +15541,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -15416,7 +15549,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -15424,7 +15557,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -15432,7 +15565,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -15440,7 +15573,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>23</v>
       </c>
@@ -15448,7 +15581,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -15456,7 +15589,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -15464,7 +15597,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>26</v>
       </c>
@@ -15472,7 +15605,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>27</v>
       </c>
@@ -15480,7 +15613,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>29</v>
       </c>
@@ -15488,7 +15621,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>31</v>
       </c>
@@ -15496,7 +15629,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -15504,7 +15637,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -15512,7 +15645,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -15520,7 +15653,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -15528,7 +15661,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>63</v>
       </c>
@@ -15536,7 +15669,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -15544,7 +15677,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -15552,7 +15685,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
